--- a/Hitachi_B1Spec/ConstDB/ConstDB.xlsx
+++ b/Hitachi_B1Spec/ConstDB/ConstDB.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vuloi\Desktop\Loi\GitHub\CICD_Test\Hitachi_B1Spec\ConstDB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vuloi\Desktop\Loi\GitHub\CICD_Test\Spec\Hitachi_B1Spec\ConstDB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FB6BD82-BA4E-4495-9CF5-A3495E1E9230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1CFD29F-1B0E-401D-AC00-EA73F73C8C33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -692,7 +692,7 @@
         <v>23</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">

--- a/Hitachi_B1Spec/ConstDB/ConstDB.xlsx
+++ b/Hitachi_B1Spec/ConstDB/ConstDB.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vuloi\Desktop\Loi\GitHub\CICD_Test\Spec\Hitachi_B1Spec\ConstDB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vuloi\Desktop\Loi\Coding\02_GitHub\CICD_Test\Spec\Hitachi_B1Spec\ConstDB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1CFD29F-1B0E-401D-AC00-EA73F73C8C33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCFF2125-3760-4DED-AB15-B39696D8D0AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-113" yWindow="-113" windowWidth="24267" windowHeight="13023" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -481,7 +481,7 @@
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="G3" s="1">
         <v>1</v>
@@ -502,7 +502,7 @@
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1">
-        <v>2050</v>
+        <v>3000</v>
       </c>
       <c r="G4" s="1">
         <v>1</v>
@@ -522,7 +522,7 @@
         <v>56</v>
       </c>
       <c r="G5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -539,7 +539,7 @@
         <v>78</v>
       </c>
       <c r="G6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -556,7 +556,7 @@
         <v>43</v>
       </c>
       <c r="G7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -573,7 +573,7 @@
         <v>45</v>
       </c>
       <c r="G8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -590,7 +590,7 @@
         <v>22</v>
       </c>
       <c r="G9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -692,7 +692,7 @@
         <v>23</v>
       </c>
       <c r="G15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
